--- a/data/seed/portfolio/L-2025-2970/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-2970/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J180"/>
+  <dimension ref="A1:J136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,37 +540,37 @@
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n">
-        <v>1759000</v>
-      </c>
+      <c r="C8" s="2" t="n">
+        <v>11973000</v>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4421 01.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №164/26</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>98059000</v>
+        <v>84327000</v>
       </c>
     </row>
     <row r="9">
@@ -582,141 +582,136 @@
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>6019000</v>
+        <v>12667000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №290/26 от 02.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2808</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>104078000</v>
+        <v>96994000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>1095000</v>
+        <v>3311000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4117 от 02.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №116/26 от 03.07.2026</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>105173000</v>
+        <v>100305000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46205</v>
+        <v>46208</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>981000</v>
-      </c>
+      <c r="C11" s="2" t="n">
+        <v>28300000</v>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>234202002</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2970)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>16307000218496025417</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №45/26 от 02.07.2026</t>
+          <t>Kredit shartnomasi L-2025-2970 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>106154000</v>
+        <v>72005000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>9978000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>13483000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -726,37 +721,37 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №44/26</t>
+          <t>Shartnoma №195/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>96176000</v>
+        <v>85488000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>13865000</v>
-      </c>
-      <c r="D13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n">
+        <v>9983000</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -766,126 +761,131 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №231/26</t>
+          <t>Оплата за товар по с/ф №1423 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>82311000</v>
+        <v>95471000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>20592000</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n">
+        <v>535000</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bahor Logistik AJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>345396929</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000438245116001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №4866</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4240 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>61719000</v>
+        <v>96006000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>2341000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>4181000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №291/26 от 03.07.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №651</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>64060000</v>
+        <v>91825000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>28300000</v>
+        <v>7751000</v>
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2970)</t>
+          <t>Bekobod Yog'och AJ</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>392200783</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>16307000218496025417</t>
+          <t>20208000686785925001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2970 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №51/26, QQS bilan</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>35760000</v>
+        <v>84074000</v>
       </c>
     </row>
     <row r="17">
@@ -895,183 +895,178 @@
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>3096000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>25459000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>234202002</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №224/26, НДС 12%</t>
+          <t>Iyun oyi uchun ish haqi, reestr №7459</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>38856000</v>
+        <v>58615000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>1290000</v>
+        <v>2767000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №222/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6099 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>40146000</v>
+        <v>61382000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>826000</v>
+        <v>1275000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №17/26, НДС 12%</t>
+          <t>Shartnoma №131/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>40972000</v>
+        <v>62657000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>3334000</v>
+        <v>2028000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahor Logistik AJ</t>
+          <t>Zafar Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>345396929</t>
+          <t>225839144</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000438245116001</t>
+          <t>20208000692050332001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2709</t>
+          <t>Ijara haqi iyul oyi uchun, shartnoma №49/21</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>37638000</v>
+        <v>60629000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>4860000</v>
+        <v>4303000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1081,272 +1076,277 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lovh/f №3870</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №86/26, QQS bilan</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>32778000</v>
+        <v>56326000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>6431000</v>
-      </c>
-      <c r="D22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n">
+        <v>1445000</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Angren Mebel XK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>310233070</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000411555444001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №50/26 ОТ 06.07.2026, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №296/26, QQS 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>26347000</v>
+        <v>57771000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>25459000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>201029000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Bahor Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №9895</t>
+          <t>Предоплата за товар по дог. №283/26 от 10.07.2026</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>888000</v>
+        <v>258800000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n"/>
       <c r="D24" s="2" t="n">
-        <v>516000</v>
+        <v>518000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bog'ishamol Metall MChJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>202157750</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000566071121001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8854 ОТ 07.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №619 13.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1404000</v>
+        <v>259318000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46210</v>
+        <v>46219</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>4537000</v>
+        <v>3472000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №9611</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-3133000</v>
+        <v>255846000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46210</v>
+        <v>46219</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10369000</v>
+        <v>3472000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Afrosiyob Savdo AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>222583914</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000969205033001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товары соглано счет-фактуре №6137</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-13502000</v>
+        <v>252374000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>2803000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>4572000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Termiz Metall AJ</t>
+          <t>Lazzat Metall AJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>326200463</t>
+          <t>202373897</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000302125123001</t>
+          <t>20208000975203269001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5676 от 08.07.2026, в т.ч. НДС 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №26/26, QQS BILAN</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>-10699000</v>
+        <v>247802000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>1245000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>8576000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bekobod Yog'och AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>392200783</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000686785925001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1356,157 +1356,157 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №117/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №76/26</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>-9454000</v>
+        <v>239226000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46211</v>
+        <v>46223</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>36777000</v>
+        <v>146251000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Lazzat Metall AJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>202373897</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>20208000975203269001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №100/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №1/26</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>-46231000</v>
+        <v>92975000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>3069000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>3402000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5487 от 09.07.2026, в т.ч. НДС 12%</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>-43162000</v>
+        <v>89573000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>733000</v>
+        <v>33246000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Bog'ishamol Metall MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>202157750</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000566071121001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3224 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1391</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>-42429000</v>
+        <v>122819000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46212</v>
+        <v>46226</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>2028000</v>
+        <v>1268000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>398422937</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000470825636001</t>
+          <t>20208000899842293001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1516,117 +1516,117 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №13/21</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>-44457000</v>
+        <v>121551000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46213</v>
+        <v>46230</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>1271000</v>
+        <v>1017000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Marg'ilon Plastik MChJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>311021577</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000075660711001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7889 10.07.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №98/26, QQS 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>-43186000</v>
+        <v>122568000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n"/>
       <c r="D34" s="2" t="n">
-        <v>12215000</v>
+        <v>630000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №23/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №8/26, QQS 12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>-30971000</v>
+        <v>123198000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46216</v>
+        <v>46231</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>1092000</v>
+        <v>921000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Barakali Oziq-ovqat Savdo MChJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>309907313</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000409788783001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1636,157 +1636,152 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №1/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №11/26, QQS 12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>-29879000</v>
+        <v>124119000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46216</v>
+        <v>46232</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>761000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>4013000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Denov Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>317786145</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000201962342001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №206/26 от 13.07.2026</t>
+          <t>Tovarlar uchun to'lov h/f №6917</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>-29118000</v>
+        <v>120106000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46216</v>
+        <v>46233</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>613000</v>
+        <v>636000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Marg'ilon Plastik MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>311021577</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000075660711001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2413 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5839 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>-28505000</v>
+        <v>120742000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46216</v>
+        <v>46233</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n">
-        <v>520000</v>
-      </c>
+      <c r="C38" s="2" t="n">
+        <v>31310000</v>
+      </c>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Termiz Metall AJ</t>
+          <t>Bekobod Yog'och AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>326200463</t>
+          <t>392200783</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000302125123001</t>
+          <t>20208000686785925001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №162/26 от 13.07.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №223/26</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>-27985000</v>
+        <v>89432000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46216</v>
+        <v>46234</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>4098000</v>
+        <v>300000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Guliston Tur Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>307842926</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000573246156001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1796,357 +1791,352 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №268/26, QQS bilan</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>-32083000</v>
+        <v>89132000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>5388000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>15474000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №5653</t>
+          <t>Mahsulot uchun to'lov, shartnoma №176/26, QQS 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>-37471000</v>
+        <v>104606000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46217</v>
+        <v>46237</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>3472000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>14740000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>320046303</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000212512384001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Tovar uchun to'lov, h/f №110 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>-40943000</v>
+        <v>119346000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46217</v>
+        <v>46237</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>3472000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>9432000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1891</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>-44415000</v>
+        <v>128778000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46217</v>
+        <v>46237</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>7364000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>2581000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bahor Logistik AJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>345396929</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000438245116001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №191/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5532</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>-51779000</v>
+        <v>131359000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46219</v>
+        <v>46237</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>937000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>10667000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Termiz Metall AJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>326200463</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000302125123001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9813 16.07.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №210/26</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>-50842000</v>
+        <v>120692000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46219</v>
+        <v>46238</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>867000</v>
+        <v>3574000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №213</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1651 04.0.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>-49975000</v>
+        <v>124266000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46220</v>
+        <v>46239</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>1623000</v>
+        <v>7696000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shodlik Plastik MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>235618050</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000242102320001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9759 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №8682 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>-48352000</v>
+        <v>131962000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46220</v>
+        <v>46239</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>897000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>28300000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>301904136</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2970)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>16307000218496025417</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7500 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-2970 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>-47455000</v>
+        <v>103662000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46220</v>
+        <v>46240</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>46372000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>2664000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2156,237 +2146,232 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №285/26</t>
+          <t>Shartnoma №200/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>-93827000</v>
+        <v>106326000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46223</v>
+        <v>46240</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>193884000</v>
+        <v>2369000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Termiz Metall AJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>326200463</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000302125123001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №1/26 от 20.07.2026</t>
+          <t>Оплата по с/ф №866 за поставленный товар</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>100057000</v>
+        <v>108695000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46224</v>
+        <v>46240</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>5559000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>24761000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Xiva Ip-Kalava MChJ</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>209631338</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000540524566001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №246 21.07.2026, QQS bilan</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>105616000</v>
+        <v>83934000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46224</v>
+        <v>46241</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>554000</v>
+        <v>20552000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Shartnoma №177/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7925</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>106170000</v>
+        <v>104486000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46224</v>
+        <v>46241</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
-      <c r="C52" s="2" t="n">
-        <v>2988000</v>
-      </c>
-      <c r="D52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n">
+        <v>10867000</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №161/26</t>
+          <t>Shartnoma №223/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>103182000</v>
+        <v>115353000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46225</v>
+        <v>46244</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>946000</v>
+        <v>2819000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barakali Oziq-ovqat Savdo MChJ</t>
+          <t>Oqtosh Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>309907313</t>
+          <t>384292665</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000409788783001</t>
+          <t>20208000324615670001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Shartnoma №288/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №986</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>104128000</v>
+        <v>118172000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46225</v>
+        <v>46244</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>476000</v>
+        <v>2332000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Xiva Ip-Kalava MChJ</t>
+          <t>Bog'ishamol Metall MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>209631338</t>
+          <t>202157750</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000540524566001</t>
+          <t>20208000566071121001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2396,77 +2381,77 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №95/26 от 22.07.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6699 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>104604000</v>
+        <v>120504000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46226</v>
+        <v>46244</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>3294000</v>
+        <v>1973000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>225839144</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000692050332001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>101310000</v>
+        <v>118531000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46226</v>
+        <v>46245</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>4879000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>6382000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>361805092</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000210232009001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2476,197 +2461,197 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №60/26 от 23.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1450</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>96431000</v>
+        <v>124913000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>4398000</v>
+        <v>4462000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Gulshan Non MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>269688547</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000499852264001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №196/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №153/26, QQS 12%</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>100829000</v>
+        <v>129375000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>2616000</v>
+        <v>3621000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SHARTNOMA №122/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за товар по счет-фактуре №5368 от 11.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>103445000</v>
+        <v>132996000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46227</v>
+        <v>46245</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>2544000</v>
+        <v>3552000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №32/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №159/26, НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>105989000</v>
+        <v>136548000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46227</v>
+        <v>46246</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>1268000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>9080000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000070165650001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №3391 2.08.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>104721000</v>
+        <v>145628000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>19723000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>9290000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2676,397 +2661,397 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №105/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6589 13.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>84998000</v>
+        <v>154918000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46230</v>
+        <v>46248</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>2500000</v>
+        <v>8094000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Shodlik Plastik MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>235618050</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000242102320001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1684 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №329</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>87498000</v>
+        <v>163012000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46230</v>
+        <v>46251</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n"/>
       <c r="D63" s="2" t="n">
-        <v>1676000</v>
+        <v>8178000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №148/26 от 27.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №31/26, QQS 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>89174000</v>
+        <v>171190000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46230</v>
+        <v>46251</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>1112000</v>
+        <v>3007000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2877 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartn. №123/26, QQS 12%</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>90286000</v>
+        <v>174197000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46230</v>
+        <v>46251</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>720000</v>
+        <v>2977000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bog'ishamol Metall MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>202157750</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000566071121001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7169 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №1011 17.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>91006000</v>
+        <v>177174000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46230</v>
+        <v>46251</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n">
-        <v>554000</v>
-      </c>
+      <c r="C66" s="2" t="n">
+        <v>3377000</v>
+      </c>
+      <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3310</t>
+          <t>Ijtimoiy soliq iyul 2026</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>91560000</v>
+        <v>173797000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46230</v>
+        <v>46251</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>5849000</v>
+        <v>3377000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №60/26 от 27.07.2026, НДС 12%</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>85711000</v>
+        <v>170420000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46231</v>
+        <v>46251</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n">
-        <v>1377000</v>
-      </c>
+      <c r="C68" s="2" t="n">
+        <v>10834000</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Xiva Ip-Kalava MChJ</t>
+          <t>Bekobod Yog'och AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>209631338</t>
+          <t>392200783</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000540524566001</t>
+          <t>20208000686785925001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5688 28.07.2026, QQS bilan</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №91/26</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>87088000</v>
+        <v>159586000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>840000</v>
+        <v>2841000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>361805092</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000210232009001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №2387</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №276/26, QQS 12%</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>87928000</v>
+        <v>162427000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46231</v>
+        <v>46252</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>5053000</v>
+        <v>11127000</v>
       </c>
       <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bahor Logistik AJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>345396929</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000438245116001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №52/26 от 28.07.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №26/26, QQS bilan</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>82875000</v>
+        <v>151300000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46232</v>
+        <v>46253</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>4973000</v>
+        <v>10329000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Xiva Ip-Kalava MChJ</t>
+          <t>Bog'ishamol Metall MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>209631338</t>
+          <t>202157750</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000540524566001</t>
+          <t>20208000566071121001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3076,507 +3061,517 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №124/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №8940 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>87848000</v>
+        <v>161629000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46232</v>
+        <v>46254</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>2235000</v>
+        <v>12592000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf AJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>278102330</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000054115554001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2524 от 29.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5342</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>90083000</v>
+        <v>174221000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46232</v>
+        <v>46254</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>8378000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>4343000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Farovon Farm Savdo XK</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>218455855</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000632665891001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №64/26</t>
+          <t>Shartnoma №22/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>81705000</v>
+        <v>178564000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46234</v>
+        <v>46254</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>976000</v>
+        <v>2651000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9665 от 31.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7502</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>82681000</v>
+        <v>181215000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46234</v>
+        <v>46255</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>300000</v>
+        <v>26821000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Bekobod Yog'och AJ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>392200783</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000686785925001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №166/26</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>82381000</v>
+        <v>154394000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>22024000</v>
+        <v>20801000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9232 03.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №577</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>104405000</v>
+        <v>175195000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>9271000</v>
+        <v>11698000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7834 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №24/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>113676000</v>
+        <v>186893000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>1482000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>8264000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Farovon Farm Savdo XK</t>
+          <t>Bog'ishamol Metall MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>218455855</t>
+          <t>202157750</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000632665891001</t>
+          <t>20208000566071121001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №1/26</t>
+          <t>Shartnoma №165/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>112194000</v>
+        <v>195157000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>2158000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>3352000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №137/26 от 03.08.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №49/26, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>110036000</v>
+        <v>198509000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n">
-        <v>8642000</v>
-      </c>
+      <c r="C80" s="2" t="n">
+        <v>3325000</v>
+      </c>
+      <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №137/26, НДС 12%</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>118678000</v>
+        <v>195184000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>28300000</v>
+        <v>11937000</v>
       </c>
       <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2970)</t>
+          <t>Termiz Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>16307000218496025417</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2970 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №161/26</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>90378000</v>
+        <v>183247000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46240</v>
+        <v>46258</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>16958000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>21473000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7179 за поставленный товар</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №32</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>107336000</v>
+        <v>161774000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46240</v>
+        <v>46259</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>12022000</v>
+        <v>5215000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №119/26, QQ 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6566</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>119358000</v>
+        <v>166989000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46240</v>
+        <v>46259</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>4827000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>21060000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Bekobod Yog'och AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>392200783</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000686785925001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3586,37 +3581,37 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6112 от 06.08.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №275/26</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>124185000</v>
+        <v>145929000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46240</v>
+        <v>46260</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n">
-        <v>1461000</v>
-      </c>
-      <c r="D85" s="2" t="n"/>
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n">
+        <v>21274000</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3626,192 +3621,197 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №285/26</t>
+          <t>Оплата за продукцию по дог. №95/26, НДС 12%</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>122724000</v>
+        <v>167203000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46240</v>
+        <v>46261</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>24761000</v>
+        <v>1233000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000899842293001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>97963000</v>
+        <v>165970000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46244</v>
+        <v>46261</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>7691000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>104757000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №198/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №69/26</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>105654000</v>
+        <v>61213000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46244</v>
+        <v>46262</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>1973000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>5359000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Bog'ishamol Metall MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>398422937</t>
+          <t>202157750</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000470825636001</t>
+          <t>20208000566071121001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №13/21</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3487</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>103681000</v>
+        <v>66572000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46244</v>
+        <v>46262</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>9669000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>3300000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2071</t>
+          <t>Mahsulot uchun to'lov, shartnoma №115/26, QQS 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>94012000</v>
+        <v>69872000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>22687000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>4971000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3821,437 +3821,427 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №92/26 от 10.08.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2010 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>71325000</v>
+        <v>74843000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46245</v>
+        <v>46265</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>8415000</v>
+        <v>4118000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Xiva Ip-Kalava MChJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>209631338</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000540524566001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №26/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2012 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>79740000</v>
+        <v>78961000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46245</v>
+        <v>46265</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n">
-        <v>2886000</v>
-      </c>
-      <c r="D92" s="2" t="n"/>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n">
+        <v>2267000</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Afrosiyob Savdo AJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>222583914</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000969205033001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №95/26</t>
+          <t>Оплата по с/ф №2527 за поставленный товар</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>76854000</v>
+        <v>81228000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46246</v>
+        <v>46265</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>3547000</v>
+        <v>300000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>210696885</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №181/26</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>73307000</v>
+        <v>80928000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46246</v>
+        <v>46266</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>4941000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>20908000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Namangan Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>381023738</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000789752032001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6245</t>
+          <t>Shartnoma №157/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>68366000</v>
+        <v>101836000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46248</v>
+        <v>46267</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>20832000</v>
+        <v>37561000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2932 от 14.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5394</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>89198000</v>
+        <v>139397000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46248</v>
+        <v>46270</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>3377000</v>
+        <v>28300000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-2970)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000218496025417</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июль</t>
+          <t>Kredit shartnomasi L-2025-2970 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>85821000</v>
+        <v>111097000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46248</v>
+        <v>46272</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n">
-        <v>3377000</v>
-      </c>
-      <c r="D97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n">
+        <v>24437000</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Lazzat Savdo MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361805092</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000210232009001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>НДФЛ за июль 2026</t>
+          <t>Shartnoma №66/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>82444000</v>
+        <v>135534000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46251</v>
+        <v>46272</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>8536000</v>
+        <v>4776000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8254 за поставленный товар</t>
+          <t>Tovar uchun to'lov, h/f №7727 07.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>90980000</v>
+        <v>140310000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46251</v>
+        <v>46272</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>1360000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>4689000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Angren Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>320046303</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000212512384001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №258/26, QQS bilan</t>
+          <t>Shartnoma №123/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>89620000</v>
+        <v>144999000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46251</v>
+        <v>46272</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>4563000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>4393000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3449</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2805</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>85057000</v>
+        <v>149392000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46251</v>
+        <v>46272</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>76675000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>4034000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4261,597 +4251,592 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №122/26, QQS bilan</t>
+          <t>Предоплата за товар по договору №233/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>8382000</v>
+        <v>153426000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46252</v>
+        <v>46272</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>81374000</v>
+        <v>4024000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №29/26, QQS 12%</t>
+          <t>Shartnoma №180/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>89756000</v>
+        <v>157450000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46252</v>
+        <v>46272</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>16679000</v>
+        <v>3691000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shodlik Plastik MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>235618050</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000242102320001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №295/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6613 07.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>106435000</v>
+        <v>161141000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46253</v>
+        <v>46272</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>38804000</v>
+        <v>1853000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Zafar Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>225839144</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>20208000692050332001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №43/26 от 19.08.2026, НДС 12%</t>
+          <t>Аренда помещения за сентябрь, дог. №49/21</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>67631000</v>
+        <v>159288000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46255</v>
+        <v>46272</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>1611000</v>
+        <v>21427000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Saodat Polimer MChJ</t>
+          <t>Bekobod Yog'och AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>300261865</t>
+          <t>392200783</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000246794011001</t>
+          <t>20208000686785925001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2073</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №2/26</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>66020000</v>
+        <v>137861000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46255</v>
+        <v>46272</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>3397000</v>
+        <v>23258000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Avgust oyi uchun ish haqi, reestr №4240</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>62623000</v>
+        <v>114603000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46258</v>
+        <v>46274</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>8285000</v>
+        <v>27487000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
+          <t>Оплата по с/ф №3442 за поставленный товар</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>70908000</v>
+        <v>142090000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46258</v>
+        <v>46276</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>1233000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>7859000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000070165650001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Предоплата за товар по договору №103/26 от 11.09.2026</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>69675000</v>
+        <v>149949000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46258</v>
+        <v>46276</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>3152000</v>
+        <v>6520000</v>
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Guliston Tur Servis MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>307842926</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000573246156001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №101/26</t>
+          <t>Tovarlar uchun to'lov h/f №5975</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>66523000</v>
+        <v>143429000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46258</v>
+        <v>46279</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>3845000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>4381000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bahor Logistik AJ</t>
+          <t>Bog'ishamol Agro MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>345396929</t>
+          <t>290413680</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000438245116001</t>
+          <t>20208000499573938001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №258/26 от 24.08.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9456</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>62678000</v>
+        <v>147810000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46258</v>
+        <v>46279</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>3958000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>4362000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Oqtosh Ip-Kalava MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>384292665</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000324615670001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №70/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3274</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>58720000</v>
+        <v>152172000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46258</v>
+        <v>46279</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>7260000</v>
+        <v>3172000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Guliston Tur Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>307842926</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000573246156001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №292/26 ОТ 24.08.2026, НДС 12%</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>51460000</v>
+        <v>149000000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46260</v>
+        <v>46279</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>28842000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>3172000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №240/26 от 26.08.2026</t>
+          <t>JISMONIY SHAXSLAR DAROMAD SOLIG'I AVGUST 2026</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>80302000</v>
+        <v>145828000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46261</v>
+        <v>46279</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>12669000</v>
+        <v>8614000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bekobod Yog'och AJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>392200783</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000686785925001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3805</t>
+          <t>Предоплата за материалы по дог. №159/26</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>67633000</v>
+        <v>137214000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46262</v>
+        <v>46279</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n">
-        <v>12295000</v>
-      </c>
+      <c r="C115" s="2" t="n">
+        <v>70721000</v>
+      </c>
+      <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Xiva Ip-Kalava MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>209631338</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000540524566001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9613 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №108/26</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>79928000</v>
+        <v>66493000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46262</v>
+        <v>46280</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>4168000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>9341000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4861,2496 +4846,751 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8791</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1840</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>75760000</v>
+        <v>75834000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>16358000</v>
+        <v>11433000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6091</t>
+          <t>Yetkazilgan tovar ucun to'lov h/f №5050</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>92118000</v>
+        <v>87267000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46265</v>
+        <v>46281</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>8552000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Bahor Mato MChJ</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Shartnoma №31/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>91818000</v>
+        <v>95819000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46265</v>
+        <v>46286</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>1478000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>3758000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №7380</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4720 21.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>90340000</v>
+        <v>99577000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46265</v>
+        <v>46286</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>8245000</v>
+        <v>3122000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>313923866</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000770850864001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №81/26 от 31.08.2026, НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за август</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>82095000</v>
+        <v>96455000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46266</v>
+        <v>46286</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>1639000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>17923000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Lazzat Metall AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>202373897</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000975203269001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8476 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №36/26</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>83734000</v>
+        <v>78532000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46268</v>
+        <v>46286</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>6465000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>37987000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №75/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №37/26</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>90199000</v>
+        <v>40545000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46268</v>
+        <v>46287</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>4107000</v>
+        <v>5732000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Bog'ishamol Metall MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>202157750</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000566071121001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №64/26 от 03.09.2026</t>
+          <t>Оплата по счет-фактуре №850 за поставленный товар</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>94306000</v>
+        <v>46277000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46268</v>
+        <v>46288</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>2761000</v>
+        <v>28658000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Ilhom Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>390731334</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000978878347001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №141/26 от 03.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4892 23.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>97067000</v>
+        <v>74935000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46269</v>
+        <v>46289</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>4919000</v>
+        <v>14112000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №2586 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Shartnoma №71/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>101986000</v>
+        <v>89047000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46269</v>
+        <v>46293</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n"/>
       <c r="D126" s="2" t="n">
-        <v>2056000</v>
+        <v>7446000</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Marg'ilon Plastik MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>311021577</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000075660711001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9036 от 04.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9405 28.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>104042000</v>
+        <v>96493000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46269</v>
+        <v>46293</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>12794000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>4528000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Durdona Mebel MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>210696885</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000724998522001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №71/26</t>
+          <t>Оплата за товар по счет-фактуре №8825 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>91248000</v>
+        <v>101021000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46270</v>
+        <v>46293</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>28300000</v>
+        <v>1158000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-2970)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>16307000218496025417</t>
+          <t>20208000899842293001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-2970 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Eletr energiyasi uchun to'lov sentyabr</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>62948000</v>
+        <v>99863000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46272</v>
+        <v>46293</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>14435000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>27965000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Barakali Oziq-ovqat Savdo MChJ</t>
+          <t>Bekobod Yog'och AJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>309907313</t>
+          <t>392200783</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000409788783001</t>
+          <t>20208000686785925001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9088 07.09.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №5427</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>77383000</v>
+        <v>71898000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46272</v>
+        <v>46294</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>12564000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>6283000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Zafar Meva Eksport MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>234202002</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000919374702001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1540 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №245/26, QQS bilan</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>89947000</v>
+        <v>65615000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>5808000</v>
+        <v>8899000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Bahor Mato MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>220200299</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000937470229001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №14/26 от 07.09.2026</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №8/26, QQS 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>95755000</v>
+        <v>74514000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>4202000</v>
+        <v>5146000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Bog'ishamol Metall MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>202157750</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000566071121001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №216/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №257/26 от 30.09.2026</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>99957000</v>
+        <v>79660000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>4143000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Shodlik Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>235618050</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000242102320001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №131/26 от 07.09.2026</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>104100000</v>
+        <v>79360000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46272</v>
+        <v>46295</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>2251000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>3660000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
+          <t>Termiz Qurilish MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>301904136</t>
+          <t>345585556</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000044995739001</t>
+          <t>20208000266589166001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8440</t>
+          <t>Tovarlar uchun to'lov h/f №1899</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>106351000</v>
+        <v>75700000</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B135" t="n">
-        <v>227</v>
-      </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>2186000</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №4461 от 07.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J135" s="2" t="n">
-        <v>108537000</v>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="n">
+        <v>841388000</v>
+      </c>
+      <c r="D135" s="4" t="n">
+        <v>820788000</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B136" t="n">
-        <v>228</v>
-      </c>
-      <c r="C136" s="2" t="n">
-        <v>15031000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Durdona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>210696885</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>20208000724998522001</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №4803</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="n">
-        <v>93506000</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B137" t="n">
-        <v>229</v>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>20999000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Durdona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>210696885</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>20208000724998522001</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №186/26</t>
-        </is>
-      </c>
-      <c r="J137" s="2" t="n">
-        <v>72507000</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="n">
-        <v>46272</v>
-      </c>
-      <c r="B138" t="n">
-        <v>230</v>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>23258000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №4730</t>
-        </is>
-      </c>
-      <c r="J138" s="2" t="n">
-        <v>49249000</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B139" t="n">
-        <v>231</v>
-      </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>4413000</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №88/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J139" s="2" t="n">
-        <v>53662000</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B140" t="n">
-        <v>232</v>
-      </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>1962000</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №5534 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="n">
-        <v>55624000</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B141" t="n">
-        <v>233</v>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>1853000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Omad Qurilish AJ</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>398422937</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>20208000470825636001</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>Арендная плата за сентябрь 2026 г. по дог. №13/21</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="n">
-        <v>53771000</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B142" t="n">
-        <v>234</v>
-      </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>3802000</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ №111/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J142" s="2" t="n">
-        <v>57573000</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B143" t="n">
-        <v>235</v>
-      </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>2802000</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Xiva Ip-Kalava MChJ</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>209631338</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>20208000540524566001</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по дог. №277/26 от 09.09.2026</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="n">
-        <v>60375000</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="n">
-        <v>46274</v>
-      </c>
-      <c r="B144" t="n">
-        <v>236</v>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>29278000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Durdona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>210696885</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>20208000724998522001</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №122/26</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>31097000</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="n">
-        <v>46275</v>
-      </c>
-      <c r="B145" t="n">
-        <v>237</v>
-      </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>7537000</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №6799 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>38634000</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="B146" t="n">
-        <v>238</v>
-      </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>2335000</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №2142 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>40969000</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B147" t="n">
-        <v>239</v>
-      </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>1722000</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>301904136</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>20208000044995739001</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №174/26 от 14.09.2026</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>42691000</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B148" t="n">
-        <v>240</v>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>3172000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>IJTIMOIY SOLIQ AVGUST 2026</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>39519000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="n">
-        <v>46279</v>
-      </c>
-      <c r="B149" t="n">
-        <v>241</v>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>3172000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>НДФЛ за вгуст 2026</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n">
-        <v>36347000</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="n">
-        <v>46280</v>
-      </c>
-      <c r="B150" t="n">
-        <v>242</v>
-      </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>14629000</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Termiz Metall AJ</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>326200463</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>20208000302125123001</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №63/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>50976000</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B151" t="n">
-        <v>243</v>
-      </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>3688000</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Bog'ishamol Poligraf AJ</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>278102330</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20208000054115554001</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Предоплата за това по договору №52/26 от 16.09.2026</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>54664000</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="n">
-        <v>46281</v>
-      </c>
-      <c r="B152" t="n">
-        <v>244</v>
-      </c>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n">
-        <v>1572000</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №67/26 от 16.09.2026</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>56236000</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B153" t="n">
-        <v>245</v>
-      </c>
-      <c r="C153" s="2" t="n"/>
-      <c r="D153" s="2" t="n">
-        <v>4124000</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Barakali Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>309907313</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000409788783001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Shartnoma №265/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>60360000</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B154" t="n">
-        <v>246</v>
-      </c>
-      <c r="C154" s="2" t="n"/>
-      <c r="D154" s="2" t="n">
-        <v>2874000</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №2550 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>63234000</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B155" t="n">
-        <v>247</v>
-      </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>1726000</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №270/26 от 17.09.2026</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>64960000</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>46282</v>
-      </c>
-      <c r="B156" t="n">
-        <v>248</v>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>33973000</v>
-      </c>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Tong Avto Ehtiyot MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>313923866</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000770850864001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Оплата за упаковочные материалы, с/ф №2632</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>30987000</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B157" t="n">
-        <v>249</v>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>5735000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №3348 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>36722000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B158" t="n">
-        <v>250</v>
-      </c>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n">
-        <v>1880000</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9656 18.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>38602000</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="n">
-        <v>46283</v>
-      </c>
-      <c r="B159" t="n">
-        <v>251</v>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>9085000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Durdona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>210696885</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000724998522001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №136/26</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>29517000</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B160" t="n">
-        <v>252</v>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>12470000</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3955 21.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>41987000</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B161" t="n">
-        <v>253</v>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>6104000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №6786 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>48091000</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B162" t="n">
-        <v>254</v>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>4012000</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Termiz Metall AJ</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>326200463</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000302125123001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №182/26 от 21.09.2026</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>52103000</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B163" t="n">
-        <v>255</v>
-      </c>
-      <c r="C163" s="2" t="n"/>
-      <c r="D163" s="2" t="n">
-        <v>2944000</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Xiva Ip-Kalava MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>209631338</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000540524566001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1749</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>55047000</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B164" t="n">
-        <v>256</v>
-      </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>2025000</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>301904136</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000044995739001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №6926 от 21.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>57072000</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B165" t="n">
-        <v>257</v>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>3085000</v>
-      </c>
-      <c r="D165" s="2" t="n"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Уплата налога на добавленную стоимость за август</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>53987000</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B166" t="n">
-        <v>258</v>
-      </c>
-      <c r="C166" s="2" t="n"/>
-      <c r="D166" s="2" t="n">
-        <v>2215000</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Barakali Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>309907313</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>20208000409788783001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Shartnoma №252/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n">
-        <v>56202000</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="n">
-        <v>46288</v>
-      </c>
-      <c r="B167" t="n">
-        <v>259</v>
-      </c>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n">
-        <v>2174000</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Bekobod Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>301904136</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>20208000044995739001</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №1444 от 23.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J167" s="2" t="n">
-        <v>58376000</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B168" t="n">
-        <v>260</v>
-      </c>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n">
-        <v>2311000</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>Shartnoma №55/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J168" s="2" t="n">
-        <v>60687000</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B169" t="n">
-        <v>261</v>
-      </c>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n">
-        <v>2882000</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Termiz Metall AJ</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>326200463</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>20208000302125123001</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №158/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="n">
-        <v>63569000</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B170" t="n">
-        <v>262</v>
-      </c>
-      <c r="C170" s="2" t="n"/>
-      <c r="D170" s="2" t="n">
-        <v>51425000</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №7298 от 28.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J170" s="2" t="n">
-        <v>114994000</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B171" t="n">
-        <v>263</v>
-      </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>9105000</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Shodlik Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>235618050</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>20208000242102320001</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №5/26 ОТ 28.09.2026</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="n">
-        <v>124099000</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B172" t="n">
-        <v>264</v>
-      </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>2678000</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Marg'ilon Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>311021577</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>20208000075660711001</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №224/26 от 28.09.2026</t>
-        </is>
-      </c>
-      <c r="J172" s="2" t="n">
-        <v>126777000</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B173" t="n">
-        <v>265</v>
-      </c>
-      <c r="C173" s="2" t="n"/>
-      <c r="D173" s="2" t="n">
-        <v>1888000</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Zafar Meva Eksport MChJ</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>234202002</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>20208000919374702001</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по дог. №97/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="n">
-        <v>128665000</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B174" t="n">
-        <v>266</v>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>1158000</v>
-      </c>
-      <c r="D174" s="2" t="n"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>20208000070165650001</t>
-        </is>
-      </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="n">
-        <v>127507000</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B175" t="n">
-        <v>267</v>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>52589000</v>
-      </c>
-      <c r="D175" s="2" t="n"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Durdona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>210696885</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>20208000724998522001</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №54/26 от 29.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="n">
-        <v>74918000</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B176" t="n">
-        <v>268</v>
-      </c>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n">
-        <v>26541000</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Xiva Ip-Kalava MChJ</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>209631338</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>20208000540524566001</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7221 30.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J176" s="2" t="n">
-        <v>101459000</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B177" t="n">
-        <v>269</v>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D177" s="2" t="n"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Bodomzor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
-        </is>
-      </c>
-      <c r="J177" s="2" t="n">
-        <v>101159000</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B178" t="n">
-        <v>270</v>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>25459000</v>
-      </c>
-      <c r="D178" s="2" t="n"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Durdona Mebel MChJ</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>210696885</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>20208000724998522001</t>
-        </is>
-      </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Оплата за транспортные услуги по договору №133/26</t>
-        </is>
-      </c>
-      <c r="J178" s="2" t="n">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="n">
         <v>75700000</v>
       </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="n">
-        <v>835271000</v>
-      </c>
-      <c r="D179" s="4" t="n">
-        <v>814671000</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="n">
-        <v>75700000</v>
-      </c>
-      <c r="D180" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
